--- a/Anumoy_Pathak_RedBus/User_Story_Restructured.xlsx
+++ b/Anumoy_Pathak_RedBus/User_Story_Restructured.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d6a5426fd29e00d/Desktop/Sprint/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d6a5426fd29e00d/Desktop/Anumoy_Pathak_RedBus/Anumoy_Pathak_RedBus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{7BF77080-D501-4069-B178-341DA633E798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55F0B314-3755-4C35-8E0A-2226362E1184}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{7BF77080-D501-4069-B178-341DA633E798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AC25165-8B8A-4048-9485-F4C7AC0F3798}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -123,9 +123,6 @@
     <t>Story 4</t>
   </si>
   <si>
-    <t>User enters passenger details for booking</t>
-  </si>
-  <si>
     <t>Enter passenger name</t>
   </si>
   <si>
@@ -141,9 +138,6 @@
     <t>Show error for invalid age input</t>
   </si>
   <si>
-    <t>Auto-fill passenger details from saved profile</t>
-  </si>
-  <si>
     <t>Sub story 3</t>
   </si>
   <si>
@@ -169,6 +163,12 @@
   </si>
   <si>
     <t>View bus ratings and reviews</t>
+  </si>
+  <si>
+    <t>Fill the contact details and proceed to payment page</t>
+  </si>
+  <si>
+    <t>User enters passenger details for booking and proceed to payment</t>
   </si>
 </sst>
 </file>
@@ -427,6 +427,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -671,10 +675,10 @@
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>3</v>
@@ -682,10 +686,10 @@
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>8</v>
@@ -693,7 +697,7 @@
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>16</v>
@@ -704,10 +708,10 @@
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>7</v>
@@ -748,7 +752,7 @@
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>20</v>
@@ -759,7 +763,7 @@
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>21</v>
@@ -770,7 +774,7 @@
     </row>
     <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>22</v>
@@ -814,7 +818,7 @@
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>26</v>
@@ -825,7 +829,7 @@
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>27</v>
@@ -836,7 +840,7 @@
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>28</v>
@@ -847,7 +851,7 @@
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>29</v>
@@ -858,7 +862,7 @@
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>30</v>
@@ -867,12 +871,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>3</v>
@@ -883,7 +887,7 @@
         <v>5</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>3</v>
@@ -894,7 +898,7 @@
         <v>6</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>3</v>
@@ -902,10 +906,10 @@
     </row>
     <row r="27" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>3</v>
@@ -913,10 +917,10 @@
     </row>
     <row r="28" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>3</v>
@@ -924,10 +928,10 @@
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>7</v>
@@ -935,13 +939,13 @@
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
